--- a/Result/profitability/1584.xlsx
+++ b/Result/profitability/1584.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01875</v>
+        <v>-0.02375</v>
       </c>
       <c r="N2" t="n">
-        <v>11.89625</v>
+        <v>11.62875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05624999999999999</v>
+        <v>-0.02625</v>
       </c>
       <c r="N3" t="n">
-        <v>11.01625</v>
+        <v>11.52</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03625</v>
+        <v>-0.0575</v>
       </c>
       <c r="N4" t="n">
-        <v>11.66</v>
+        <v>12.0975</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.045</v>
       </c>
       <c r="N5" t="n">
-        <v>9.772500000000001</v>
+        <v>11.02125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05624999999999999</v>
+        <v>-0.0675</v>
       </c>
       <c r="N6" t="n">
-        <v>9.943750000000001</v>
+        <v>11.29</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.15625</v>
+        <v>-0.17</v>
       </c>
       <c r="N7" t="n">
-        <v>8.317500000000001</v>
+        <v>8.963750000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>-0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.22375</v>
+        <v>-0.2225</v>
       </c>
       <c r="N8" t="n">
-        <v>7.425000000000001</v>
+        <v>8.4725</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1584</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>571</v>
+      </c>
+      <c r="D75" t="n">
+        <v>462</v>
+      </c>
+      <c r="E75" t="n">
+        <v>110</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>57</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.91%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="J75" t="n">
+        <v>28</v>
+      </c>
+      <c r="K75" t="n">
+        <v>23</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.2175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1111111111111112</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.379999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.7759259259259257</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.454545454545455</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.087051142546246</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
